--- a/app/static/students.xlsx
+++ b/app/static/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\111\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CB6A721-758F-47C9-B7CF-BF7C538BDAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB15EAFF-B9EE-48F6-948F-C5BC96BC21E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CEC920A4-4954-4937-AD00-D9C313E12F09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1661664E-87F6-447C-9077-0C78736C0A17}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,148 +34,346 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Ism</t>
-  </si>
-  <si>
-    <t>Familiya</t>
-  </si>
-  <si>
-    <t>Abror</t>
-  </si>
-  <si>
-    <t>Alimov</t>
-  </si>
-  <si>
-    <t>Bekzod</t>
-  </si>
-  <si>
-    <t>Baxtiyorov</t>
-  </si>
-  <si>
-    <t>Sardor</t>
-  </si>
-  <si>
-    <t>Soliyev</t>
-  </si>
-  <si>
-    <t>Javohir</t>
-  </si>
-  <si>
-    <t>Jumaboyev</t>
-  </si>
-  <si>
-    <t>Madina</t>
-  </si>
-  <si>
-    <t>Maqsudova</t>
-  </si>
-  <si>
-    <t>Nigora</t>
-  </si>
-  <si>
-    <t>Nabiyeva</t>
-  </si>
-  <si>
-    <t>Rustam</t>
-  </si>
-  <si>
-    <t>Rahimov</t>
-  </si>
-  <si>
-    <t>Temur</t>
-  </si>
-  <si>
-    <t>To'rayev</t>
-  </si>
-  <si>
-    <t>Lola</t>
-  </si>
-  <si>
-    <t>Latipova</t>
-  </si>
-  <si>
-    <t>Aziz</t>
-  </si>
-  <si>
-    <t>Akramov</t>
-  </si>
-  <si>
-    <t>Jasur</t>
-  </si>
-  <si>
-    <t>Jalolov</t>
-  </si>
-  <si>
-    <t>Malika</t>
-  </si>
-  <si>
-    <t>Mansurova</t>
-  </si>
-  <si>
-    <t>Odil</t>
-  </si>
-  <si>
-    <t>Olimov</t>
-  </si>
-  <si>
-    <t>Farrux</t>
-  </si>
-  <si>
-    <t>Fayziyev</t>
-  </si>
-  <si>
-    <t>Umid</t>
-  </si>
-  <si>
-    <t>Umarov</t>
-  </si>
-  <si>
-    <t>Shahnoza</t>
-  </si>
-  <si>
-    <t>Shokirova</t>
-  </si>
-  <si>
-    <t>Bunyod</t>
-  </si>
-  <si>
-    <t>Bekmirzayev</t>
-  </si>
-  <si>
-    <t>Guli</t>
-  </si>
-  <si>
-    <t>G'aniyeva</t>
-  </si>
-  <si>
-    <t>Dilshod</t>
-  </si>
-  <si>
-    <t>Davronov</t>
-  </si>
-  <si>
-    <t>Zafar</t>
-  </si>
-  <si>
-    <t>Zokirov</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+  <si>
+    <t>oquvchi_ismi</t>
+  </si>
+  <si>
+    <t>terminal_id</t>
+  </si>
+  <si>
+    <t>ota_ona_ismi</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Abdullayev Anvar</t>
+  </si>
+  <si>
+    <t>Abdullayev Akmal</t>
+  </si>
+  <si>
+    <t>Bekmurodova Sevinch</t>
+  </si>
+  <si>
+    <t>Karimov Mansur</t>
+  </si>
+  <si>
+    <t>Rustamov Dilshod</t>
+  </si>
+  <si>
+    <t>Rustamova Gulnora</t>
+  </si>
+  <si>
+    <t>Karimova Zilola</t>
+  </si>
+  <si>
+    <t>Karimov Sanjar</t>
+  </si>
+  <si>
+    <t>Ismoilov Jalol</t>
+  </si>
+  <si>
+    <t>Ismoilova Shahnoza</t>
+  </si>
+  <si>
+    <t>Ergashev Sardor</t>
+  </si>
+  <si>
+    <t>Ergasheva Umida</t>
+  </si>
+  <si>
+    <t>Soliyev Bobur</t>
+  </si>
+  <si>
+    <t>Soliyeva Ra'no</t>
+  </si>
+  <si>
+    <t>Qodirova Madina</t>
+  </si>
+  <si>
+    <t>Qodirov Jamshid</t>
+  </si>
+  <si>
+    <t>Xolmatov Otabek</t>
+  </si>
+  <si>
+    <t>Xolmatova Lobar</t>
+  </si>
+  <si>
+    <t>Tursunova Laylo</t>
+  </si>
+  <si>
+    <t>Tursunov Alisher</t>
+  </si>
+  <si>
+    <t>Mirzayev Farhod</t>
+  </si>
+  <si>
+    <t>Mirzayeva Nigora</t>
+  </si>
+  <si>
+    <t>Olimov Jasur</t>
+  </si>
+  <si>
+    <t>Olimova Malika</t>
+  </si>
+  <si>
+    <t>Fayzullayev Sherzod</t>
+  </si>
+  <si>
+    <t>Fayzullayev Botir</t>
+  </si>
+  <si>
+    <t>Hamrayeva Guli</t>
+  </si>
+  <si>
+    <t>Hamrayev Aziz</t>
+  </si>
+  <si>
+    <t>Jo'rayev Eldor</t>
+  </si>
+  <si>
+    <t>Jo'rayeva Dildora</t>
+  </si>
+  <si>
+    <t>Eshmatov Vali</t>
+  </si>
+  <si>
+    <t>Eshmatov G'ani</t>
+  </si>
+  <si>
+    <t>Toshmatova Oydin</t>
+  </si>
+  <si>
+    <t>Toshmatov Odil</t>
+  </si>
+  <si>
+    <t>Nazarov Shohruh</t>
+  </si>
+  <si>
+    <t>Nazarova Dilfuza</t>
+  </si>
+  <si>
+    <t>Umarov Komil</t>
+  </si>
+  <si>
+    <t>Umarova Aziza</t>
+  </si>
+  <si>
+    <t>Sobirova Nilufar</t>
+  </si>
+  <si>
+    <t>Sobirov Ulug'bek</t>
+  </si>
+  <si>
+    <t>Azimov Akram</t>
+  </si>
+  <si>
+    <t>Azimova Munira</t>
+  </si>
+  <si>
+    <t>Borisov Ivan</t>
+  </si>
+  <si>
+    <t>Borisova Elena</t>
+  </si>
+  <si>
+    <t>G'ofurov Said</t>
+  </si>
+  <si>
+    <t>G'ofurova Barno</t>
+  </si>
+  <si>
+    <t>Hakimov Temur</t>
+  </si>
+  <si>
+    <t>Hakimova Lola</t>
+  </si>
+  <si>
+    <t>Karimov Diyor</t>
+  </si>
+  <si>
+    <t>Karimov Bahrom</t>
+  </si>
+  <si>
+    <t>Latipova Sarvinoz</t>
+  </si>
+  <si>
+    <t>Latipov O'tkir</t>
+  </si>
+  <si>
+    <t>Mahmudov Sanjar</t>
+  </si>
+  <si>
+    <t>Mahmudova Shoira</t>
+  </si>
+  <si>
+    <t>Nosirova Kamola</t>
+  </si>
+  <si>
+    <t>Nosirov Abduvali</t>
+  </si>
+  <si>
+    <t>Ortiqov Rustam</t>
+  </si>
+  <si>
+    <t>Ortiqova Sayyora</t>
+  </si>
+  <si>
+    <t>Po'latov Jamol</t>
+  </si>
+  <si>
+    <t>Po'latova Gulchehra</t>
+  </si>
+  <si>
+    <t>Rahimov Ibrohim</t>
+  </si>
+  <si>
+    <t>Rahimova Ozoda</t>
+  </si>
+  <si>
+    <t>Saitov Nodir</t>
+  </si>
+  <si>
+    <t>Saitova Feruza</t>
+  </si>
+  <si>
+    <t>Toirov Abror</t>
+  </si>
+  <si>
+    <t>Toirova Jamila</t>
+  </si>
+  <si>
+    <t>Usmonov Davron</t>
+  </si>
+  <si>
+    <t>Usmonova Nozima</t>
+  </si>
+  <si>
+    <t>Vohidov Alisher</t>
+  </si>
+  <si>
+    <t>Vohidova Malohat</t>
+  </si>
+  <si>
+    <t>Yo'ldoshev Bekzod</t>
+  </si>
+  <si>
+    <t>Yo'ldosheva Ra'no</t>
+  </si>
+  <si>
+    <t>Zokirov Botir</t>
+  </si>
+  <si>
+    <t>Zokirova Nafisa</t>
+  </si>
+  <si>
+    <t>Ahmedov Sarvar</t>
+  </si>
+  <si>
+    <t>Ahmedova Dinora</t>
+  </si>
+  <si>
+    <t>Boboyev Samandar</t>
+  </si>
+  <si>
+    <t>Boboyeva Zilola</t>
+  </si>
+  <si>
+    <t>Choriyev Elbek</t>
+  </si>
+  <si>
+    <t>Choriyeva Gulnora</t>
+  </si>
+  <si>
+    <t>Do'stov Sherali</t>
+  </si>
+  <si>
+    <t>Do'stova Maftuna</t>
+  </si>
+  <si>
+    <t>Egamberdiyev Otabek</t>
+  </si>
+  <si>
+    <t>Egamberdiyeva Lola</t>
+  </si>
+  <si>
+    <t>Fozilov Iskandar</t>
+  </si>
+  <si>
+    <t>Fozilova Dilshoda</t>
+  </si>
+  <si>
+    <t>G'aniyev Umid</t>
+  </si>
+  <si>
+    <t>G'aniyeva Sabina</t>
+  </si>
+  <si>
+    <t>Hasanov Shavkat</t>
+  </si>
+  <si>
+    <t>Hasanova Nigora</t>
+  </si>
+  <si>
+    <t>Inomov Mansur</t>
+  </si>
+  <si>
+    <t>Inomova Shahrizoda</t>
+  </si>
+  <si>
+    <t>Jamilov Aziz</t>
+  </si>
+  <si>
+    <t>Jamilova Lobar</t>
+  </si>
+  <si>
+    <t>Kamolov Orif</t>
+  </si>
+  <si>
+    <t>Kamolova Umida</t>
+  </si>
+  <si>
+    <t>Musayev Elyor</t>
+  </si>
+  <si>
+    <t>Musayeva Sarvinoz</t>
+  </si>
+  <si>
+    <t>Nurmatov Doniyor</t>
+  </si>
+  <si>
+    <t>Nurmatova Ra'no</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,17 +393,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -215,9 +411,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -246,39 +447,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -330,7 +531,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -441,6 +642,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -449,13 +657,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -520,45 +721,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2511E2CC-59A4-43A2-BBEC-DCC6C8142672}">
-  <dimension ref="A1:C21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99223B5-358C-4D3F-9552-A70552AB5ADF}">
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="54.44140625" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" customWidth="1"/>
+    <col min="4" max="4" width="45.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,228 +752,712 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B2" s="2">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D2" s="2">
+        <v>998901112233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="2">
+        <v>101</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D3" s="2">
+        <v>998904445566</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B4" s="2">
+        <v>102</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D4" s="2">
+        <v>998937778899</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="B5" s="2">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D5" s="2">
+        <v>998971122334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B6" s="2">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D6" s="2">
+        <v>998905566778</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B7" s="2">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D7" s="2">
+        <v>998912233445</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="2">
+        <v>106</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D8" s="2">
+        <v>998998877665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="2">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D9" s="2">
+        <v>998944455667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B10" s="2">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D10" s="2">
+        <v>998903322114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B11" s="2">
+        <v>109</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D11" s="2">
+        <v>998915544332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="B12" s="2">
+        <v>110</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D12" s="2">
+        <v>998939988776</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>1013</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="B13" s="2">
+        <v>111</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D13" s="2">
+        <v>998902233445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>1014</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="B14" s="2">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D14" s="2">
+        <v>998977766554</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>1015</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="B15" s="2">
+        <v>113</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D15" s="2">
+        <v>998991122334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>1016</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="B16" s="2">
+        <v>114</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D16" s="2">
+        <v>998904433221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>1017</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="B17" s="2">
+        <v>115</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D17" s="2">
+        <v>998918877665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>1018</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B18" s="2">
+        <v>116</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D18" s="2">
+        <v>998931122334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>1019</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="B19" s="2">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D19" s="2">
+        <v>998905544332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>1020</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="B20" s="2">
+        <v>118</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D20" s="2">
+        <v>998972233445</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>42</v>
+      </c>
+      <c r="B21" s="2">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="2">
+        <v>998993344556</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2">
+        <v>120</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="2">
+        <v>998907788990</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="2">
+        <v>121</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="2">
+        <v>998915566443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="2">
+        <v>122</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="2">
+        <v>998932233112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="2">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2">
+        <v>998901122445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="2">
+        <v>124</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="2">
+        <v>998975544667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="2">
+        <v>125</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="2">
+        <v>998994455221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2">
+        <v>126</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="2">
+        <v>998901144556</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2">
+        <v>127</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="2">
+        <v>998915577889</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2">
+        <v>128</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="2">
+        <v>998932255443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="2">
+        <v>129</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="2">
+        <v>998903366554</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="2">
+        <v>130</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="2">
+        <v>998974411223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="2">
+        <v>131</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="2">
+        <v>998992255667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="2">
+        <v>132</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="2">
+        <v>998901177889</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="2">
+        <v>133</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="2">
+        <v>998914488552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="2">
+        <v>134</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="2">
+        <v>998936633221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="2">
+        <v>135</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="2">
+        <v>998908855221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="2">
+        <v>136</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="2">
+        <v>998971144223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="2">
+        <v>137</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="2">
+        <v>998993355778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="2">
+        <v>138</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="2">
+        <v>998901155990</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="2">
+        <v>139</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="2">
+        <v>998912244668</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="2">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="2">
+        <v>998935566112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="2">
+        <v>141</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="2">
+        <v>998904477221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="2">
+        <v>142</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="2">
+        <v>998978899554</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="2">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="2">
+        <v>998991122556</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="2">
+        <v>144</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="2">
+        <v>998905588331</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="2">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="2">
+        <v>998913366992</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="2">
+        <v>146</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="2">
+        <v>998937744112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="2">
+        <v>147</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="2">
+        <v>998909988114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="2">
+        <v>148</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="2">
+        <v>998972255883</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="2">
+        <v>149</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="2">
+        <v>998994411552</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>